--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR8"/>
+  <dimension ref="A1:BU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -503,6 +503,9 @@
     <col width="22" customWidth="1" min="68" max="68"/>
     <col width="22" customWidth="1" min="69" max="69"/>
     <col width="22" customWidth="1" min="70" max="70"/>
+    <col width="32" customWidth="1" min="71" max="71"/>
+    <col width="32" customWidth="1" min="72" max="72"/>
+    <col width="32" customWidth="1" min="73" max="73"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -856,6 +859,21 @@
           <t>chargeMinPaintRange</t>
         </is>
       </c>
+      <c r="BS1" s="7" t="inlineStr">
+        <is>
+          <t>pelletCount</t>
+        </is>
+      </c>
+      <c r="BT1" s="7" t="inlineStr">
+        <is>
+          <t>muzzleMode</t>
+        </is>
+      </c>
+      <c r="BU1" s="7" t="inlineStr">
+        <is>
+          <t>semiBufferFrames</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1208,6 +1226,21 @@
           <t>float</t>
         </is>
       </c>
+      <c r="BS2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BT2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BU2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1347,7 +1380,7 @@
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>发射：机制：0全自动／1三连发／2蓄力松开发射</t>
+          <t>发射：0全自动／1三连发／2蓄力／3半自动</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
@@ -1357,7 +1390,7 @@
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>发射：每颗耗墨</t>
+          <t>发射：每次有效发射总耗墨（霰弹整组）</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
@@ -1512,7 +1545,7 @@
       </c>
       <c r="BI3" s="3" t="inlineStr">
         <is>
-          <t>涂色：水平瞄准涂地射程目标（本项目米）</t>
+          <t>涂色：水平涂地参考距离（米，新半自动为实测值）</t>
         </is>
       </c>
       <c r="BJ3" s="3" t="inlineStr">
@@ -1558,6 +1591,21 @@
       <c r="BR3" s="3" t="inlineStr">
         <is>
           <t>蓄力：点射水平涂地射程目标（米）</t>
+        </is>
+      </c>
+      <c r="BS3" s="3" t="inlineStr">
+        <is>
+          <t>发射：每次有效发射的弹丸数量</t>
+        </is>
+      </c>
+      <c r="BT3" s="3" t="inlineStr">
+        <is>
+          <t>发射：枪口模式（0单枪／1右左交替）</t>
+        </is>
+      </c>
+      <c r="BU3" s="3" t="inlineStr">
+        <is>
+          <t>发射：半自动冷却末尾点击缓存（60Hz帧）</t>
         </is>
       </c>
     </row>
@@ -1778,6 +1826,15 @@
       <c r="BR4" s="5" t="n">
         <v>0</v>
       </c>
+      <c r="BS4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n"/>
@@ -1786,22 +1843,22 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>LightShooter</t>
+          <t>DualPistolGirl</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>轻型速射枪</t>
+          <t>双持手枪</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Character/RifleGirl</t>
+          <t>Character/DualPistolGirl</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Weapon/RifleGirlRifle</t>
+          <t>Weapon/DualPistols</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
@@ -1868,16 +1925,16 @@
         <v>60</v>
       </c>
       <c r="AB5" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AF5" s="5" t="n">
         <v>2</v>
@@ -1889,7 +1946,7 @@
         <v>15</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AJ5" s="5" t="n">
         <v>1</v>
@@ -1913,7 +1970,7 @@
         <v>0.025</v>
       </c>
       <c r="AQ5" s="5" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AR5" s="5" t="n">
         <v>4</v>
@@ -1925,7 +1982,7 @@
         <v>0.66</v>
       </c>
       <c r="AU5" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AV5" s="5" t="n">
         <v>12</v>
@@ -1934,10 +1991,10 @@
         <v>8.4</v>
       </c>
       <c r="AX5" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AY5" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AZ5" s="5" t="n">
         <v>8</v>
@@ -1946,10 +2003,10 @@
         <v>40</v>
       </c>
       <c r="BB5" s="5" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="BC5" s="5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="BD5" s="5" t="n">
         <v>0.55</v>
@@ -1961,13 +2018,13 @@
         <v>0.7</v>
       </c>
       <c r="BG5" s="5" t="n">
-        <v>0.58</v>
+        <v>0.45</v>
       </c>
       <c r="BH5" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>11.6</v>
+        <v>11.75</v>
       </c>
       <c r="BJ5" s="5" t="n">
         <v>0</v>
@@ -1995,6 +2052,15 @@
       </c>
       <c r="BR5" s="5" t="n">
         <v>0</v>
+      </c>
+      <c r="BS5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU5" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2004,22 +2070,22 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>HeavyShooter</t>
+          <t>ShotgunGirl</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>重型射击枪</t>
+          <t>霰弹枪</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Character/RifleGirl</t>
+          <t>Character/ShotgunGirl</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Weapon/RifleGirlRifle</t>
+          <t>Weapon/Shotgun</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
@@ -2086,16 +2152,16 @@
         <v>60</v>
       </c>
       <c r="AB6" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC6" s="5" t="n">
-        <v>6.666666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="AF6" s="5" t="n">
         <v>2</v>
@@ -2104,10 +2170,10 @@
         <v>10</v>
       </c>
       <c r="AH6" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AI6" s="5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AJ6" s="5" t="n">
         <v>1</v>
@@ -2116,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="AL6" s="5" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AM6" s="5" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AN6" s="5" t="n">
         <v>9.800000000000001</v>
@@ -2131,7 +2197,7 @@
         <v>0.025</v>
       </c>
       <c r="AQ6" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AR6" s="5" t="n">
         <v>4</v>
@@ -2143,31 +2209,31 @@
         <v>0.66</v>
       </c>
       <c r="AU6" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV6" s="5" t="n">
         <v>12</v>
       </c>
       <c r="AW6" s="5" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="AX6" s="5" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="AY6" s="5" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="AZ6" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA6" s="5" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="BB6" s="5" t="n">
-        <v>0.65</v>
+        <v>0.24</v>
       </c>
       <c r="BC6" s="5" t="n">
-        <v>0.8</v>
+        <v>0.32</v>
       </c>
       <c r="BD6" s="5" t="n">
         <v>0.55</v>
@@ -2179,13 +2245,13 @@
         <v>0.7</v>
       </c>
       <c r="BG6" s="5" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="BH6" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="BI6" s="5" t="n">
-        <v>15.2</v>
+        <v>12.88</v>
       </c>
       <c r="BJ6" s="5" t="n">
         <v>0</v>
@@ -2213,6 +2279,15 @@
       </c>
       <c r="BR6" s="5" t="n">
         <v>0</v>
+      </c>
+      <c r="BS6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2222,22 +2297,22 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>BurstShooter</t>
+          <t>PistolGirl</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>三连发射击枪</t>
+          <t>精确手枪</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Character/RifleGirl</t>
+          <t>Character/PistolGirl</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Weapon/RifleGirlRifle</t>
+          <t>Weapon/Pistol</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
@@ -2304,16 +2379,16 @@
         <v>60</v>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AF7" s="5" t="n">
         <v>2</v>
@@ -2322,16 +2397,16 @@
         <v>10</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI7" s="5" t="n">
         <v>3.4</v>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL7" s="5" t="n">
         <v>33</v>
@@ -2349,7 +2424,7 @@
         <v>0.025</v>
       </c>
       <c r="AQ7" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AR7" s="5" t="n">
         <v>4</v>
@@ -2361,7 +2436,7 @@
         <v>0.66</v>
       </c>
       <c r="AU7" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV7" s="5" t="n">
         <v>12</v>
@@ -2370,22 +2445,22 @@
         <v>12</v>
       </c>
       <c r="AX7" s="5" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="AY7" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AZ7" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BA7" s="5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB7" s="5" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="BC7" s="5" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="BD7" s="5" t="n">
         <v>0.55</v>
@@ -2397,13 +2472,13 @@
         <v>0.7</v>
       </c>
       <c r="BG7" s="5" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="BH7" s="5" t="n">
         <v>2.4</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>14.8</v>
+        <v>14.88</v>
       </c>
       <c r="BJ7" s="5" t="n">
         <v>0</v>
@@ -2431,6 +2506,15 @@
       </c>
       <c r="BR7" s="5" t="n">
         <v>0</v>
+      </c>
+      <c r="BS7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2440,22 +2524,22 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>ChargeShooter</t>
+          <t>RocketLauncherGirl</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>蓄力狙击枪</t>
+          <t>蓄力火箭筒</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Character/RifleGirl</t>
+          <t>Character/RocketLauncherGirl</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Weapon/RifleGirlRifle</t>
+          <t>Weapon/RocketLauncher</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
@@ -2649,6 +2733,15 @@
       </c>
       <c r="BR8" s="5" t="n">
         <v>11.2</v>
+      </c>
+      <c r="BS8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1043,12 +1043,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV8"/>
+  <dimension ref="A1:BW8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="24"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="51"/>
     <col width="25" customWidth="1" min="52" max="52"/>
@@ -1061,6 +1062,7 @@
     <col width="22" customWidth="1" min="66" max="66"/>
     <col width="32" customWidth="1" min="71" max="73"/>
     <col width="32" customWidth="1" min="72" max="72"/>
+    <col width="36" customWidth="1" min="75" max="75"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1434,6 +1436,11 @@
           <t>semiBufferFrames</t>
         </is>
       </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>neutralSwimSpeed</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1806,6 +1813,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -2176,6 +2188,11 @@
       <c r="BV3" s="1" t="inlineStr">
         <is>
           <t>发射：半自动冷却末尾点击缓存（60Hz帧）</t>
+        </is>
+      </c>
+      <c r="BW3" s="1" t="inlineStr">
+        <is>
+          <t>移动恢复：无色地面潜墨速度（米/秒，须小于普通移动速度）</t>
         </is>
       </c>
     </row>
@@ -2407,6 +2424,9 @@
       <c r="BV4" t="n">
         <v>0</v>
       </c>
+      <c r="BW4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -2636,6 +2656,9 @@
       <c r="BV5" t="n">
         <v>6</v>
       </c>
+      <c r="BW5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -2865,6 +2888,9 @@
       <c r="BV6" t="n">
         <v>6</v>
       </c>
+      <c r="BW6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -3094,6 +3120,9 @@
       <c r="BV7" t="n">
         <v>6</v>
       </c>
+      <c r="BW7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -3322,6 +3351,9 @@
       </c>
       <c r="BV8" t="n">
         <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Hero" sheetId="1" r:id="rId1"/>
@@ -1504,7 +1504,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BT8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
@@ -2264,7 +2264,7 @@
         <v>15</v>
       </c>
       <c r="AD4">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AE4">
         <v>2</v>
@@ -2285,22 +2285,22 @@
         <v>0</v>
       </c>
       <c r="AK4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AL4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AN4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO4">
         <v>0.025</v>
       </c>
       <c r="AP4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -2500,22 +2500,22 @@
         <v>0</v>
       </c>
       <c r="AK5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AM5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO5">
         <v>0.025</v>
       </c>
       <c r="AP5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ5">
         <v>10</v>
@@ -2527,7 +2527,7 @@
         <v>0.66</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU5">
         <v>12</v>
@@ -2548,10 +2548,10 @@
         <v>40</v>
       </c>
       <c r="BA5">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="BB5">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="BC5">
         <v>0.55</v>
@@ -2566,7 +2566,7 @@
         <v>0.55</v>
       </c>
       <c r="BG5">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="BH5">
         <v>2.4</v>
@@ -2715,22 +2715,22 @@
         <v>0</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL6">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AM6">
+        <v>8</v>
+      </c>
+      <c r="AN6">
         <v>10</v>
-      </c>
-      <c r="AN6">
-        <v>5</v>
       </c>
       <c r="AO6">
         <v>0.025</v>
       </c>
       <c r="AP6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
         <v>10</v>
@@ -2742,7 +2742,7 @@
         <v>0.66</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6">
         <v>12</v>
@@ -2763,10 +2763,10 @@
         <v>18</v>
       </c>
       <c r="BA6">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="BB6">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="BC6">
         <v>0.55</v>
@@ -2781,7 +2781,7 @@
         <v>0.45</v>
       </c>
       <c r="BG6">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BH6">
         <v>2.4</v>
@@ -2909,7 +2909,7 @@
         <v>5</v>
       </c>
       <c r="AD7">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <v>2</v>
@@ -2930,22 +2930,22 @@
         <v>0</v>
       </c>
       <c r="AK7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AM7">
+        <v>6</v>
+      </c>
+      <c r="AN7">
         <v>10</v>
-      </c>
-      <c r="AN7">
-        <v>5</v>
       </c>
       <c r="AO7">
         <v>0.025</v>
       </c>
       <c r="AP7">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>10</v>
@@ -2957,7 +2957,7 @@
         <v>0.66</v>
       </c>
       <c r="AT7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AU7">
         <v>12</v>
@@ -2981,7 +2981,7 @@
         <v>0.8</v>
       </c>
       <c r="BB7">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="BC7">
         <v>0.55</v>
@@ -2996,7 +2996,7 @@
         <v>0.35</v>
       </c>
       <c r="BG7">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="BH7">
         <v>2.4</v>
@@ -3145,19 +3145,19 @@
         <v>0</v>
       </c>
       <c r="AK8">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AL8">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AM8">
         <v>2</v>
       </c>
       <c r="AN8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO8">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="AP8">
         <v>0.2</v>
@@ -3172,7 +3172,7 @@
         <v>0.66</v>
       </c>
       <c r="AT8">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AU8">
         <v>12</v>
@@ -3196,7 +3196,7 @@
         <v>1.5</v>
       </c>
       <c r="BB8">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BC8">
         <v>0.55</v>
@@ -3211,7 +3211,7 @@
         <v>0.65</v>
       </c>
       <c r="BG8">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="BH8">
         <v>2.4</v>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX8"/>
+  <dimension ref="A1:CM9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="4"/>
@@ -1059,6 +1059,21 @@
     <col width="30" customWidth="1" min="74" max="74"/>
     <col width="30" customWidth="1" min="75" max="75"/>
     <col width="30" customWidth="1" min="76" max="76"/>
+    <col width="28" customWidth="1" min="77" max="77"/>
+    <col width="28" customWidth="1" min="78" max="78"/>
+    <col width="28" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="80" max="80"/>
+    <col width="28" customWidth="1" min="81" max="81"/>
+    <col width="28" customWidth="1" min="82" max="82"/>
+    <col width="28" customWidth="1" min="83" max="83"/>
+    <col width="28" customWidth="1" min="84" max="84"/>
+    <col width="28" customWidth="1" min="85" max="85"/>
+    <col width="28" customWidth="1" min="86" max="86"/>
+    <col width="28" customWidth="1" min="87" max="87"/>
+    <col width="28" customWidth="1" min="88" max="88"/>
+    <col width="28" customWidth="1" min="89" max="89"/>
+    <col width="28" customWidth="1" min="90" max="90"/>
+    <col width="28" customWidth="1" min="91" max="91"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1442,6 +1457,81 @@
           <t>airSwimBraking</t>
         </is>
       </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingMinChargeFrames</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingFirstChargeFrames</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingFirstShootFrames</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingFullShootFrames</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingSlowChargeMultiplier</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingChargeMoveSpeed</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingChargeJumpSpeed</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingPostFrames</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingPitchSpread</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingSpreadBias</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingSpeedBias</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingFootEvery</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingTrailCount</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingFootRadius</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>splatlingPlayerRadius</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1824,6 +1914,81 @@
           <t>float</t>
         </is>
       </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1963,7 +2128,7 @@
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>发射：0全自动／1三连发／2蓄力／3半自动</t>
+          <t>发射：0全自动／1三连发／2蓄力松开发射／3半自动／4旋转枪</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
@@ -1973,7 +2138,7 @@
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>发射：每次有效发射总耗墨（霰弹整组）</t>
+          <t>发射：每次有效发射耗墨（霰弹整组；旋转枪每颗从预留量结算）</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr">
@@ -2204,6 +2369,81 @@
       <c r="BX3" s="1" t="inlineStr">
         <is>
           <t>空中弦化：高速下落制动（米/秒²，大于0，不产生上升）</t>
+        </is>
+      </c>
+      <c r="BY3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：最小有效蓄力帧数</t>
+        </is>
+      </c>
+      <c r="BZ3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：第一圈蓄力帧数</t>
+        </is>
+      </c>
+      <c r="CA3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：第一圈射击窗口帧数（含第0帧首弹）</t>
+        </is>
+      </c>
+      <c r="CB3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：满蓄射击窗口帧数（含末帧）</t>
+        </is>
+      </c>
+      <c r="CC3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：空中或缺墨蓄力耗时倍率（不叠乘）</t>
+        </is>
+      </c>
+      <c r="CD3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：蓄力移动速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="CE3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：蓄力起跳速度（米/秒）</t>
+        </is>
+      </c>
+      <c r="CF3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：末弹后恢复帧数</t>
+        </is>
+      </c>
+      <c r="CG3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：地面垂直散布半角（度）</t>
+        </is>
+      </c>
+      <c r="CH3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：中心散布偏向（0到1）</t>
+        </is>
+      </c>
+      <c r="CI3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：初速随机中心偏向（0到1）</t>
+        </is>
+      </c>
+      <c r="CJ3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：脚下落墨间隔（发）</t>
+        </is>
+      </c>
+      <c r="CK3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：每颗沿途最大落墨数</t>
+        </is>
+      </c>
+      <c r="CL3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：脚下落墨半径（米）</t>
+        </is>
+      </c>
+      <c r="CM3" s="1" t="inlineStr">
+        <is>
+          <t>旋转枪：命中玩家扫掠半径（米）</t>
         </is>
       </c>
     </row>
@@ -2441,6 +2681,51 @@
       <c r="BX4" t="n">
         <v>30</v>
       </c>
+      <c r="BY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -2676,6 +2961,51 @@
       <c r="BX5" t="n">
         <v>30</v>
       </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -2911,6 +3241,51 @@
       <c r="BX6" t="n">
         <v>30</v>
       </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -3146,6 +3521,51 @@
       <c r="BX7" t="n">
         <v>30</v>
       </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -3380,6 +3800,331 @@
       </c>
       <c r="BX8" t="n">
         <v>30</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MachineGunGirl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>消防栓旋转枪</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Character/MachineGunGirl</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Weapon/MachineGun</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.583333333333333</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>101.5434538419936</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>114.1240587427716</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>43.13350251695304</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.1497691059616425</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>20.21882930482174</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.437783417231768</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.572575612597246</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>17.59786995049299</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.9645130423929776</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.9645130423929776</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>7.488455298082124</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>150</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>32</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>8.237300827890337</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>47.17726837791738</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>30</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>120</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>130</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>260</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>2.291666666666667</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>2.695843907309564</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>8</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1.157415650871573</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.1684902442068478</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="4"/>
@@ -1047,6 +1047,8 @@
     <col width="23" customWidth="1" min="25" max="25"/>
     <col width="22" customWidth="1" min="26" max="50"/>
     <col width="90" customWidth="1" min="32" max="32"/>
+    <col width="24" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="34" max="34"/>
     <col width="25" customWidth="1" min="51" max="51"/>
     <col width="23" customWidth="1" min="52" max="52"/>
     <col width="22" customWidth="1" min="53" max="57"/>
@@ -1238,6 +1240,16 @@
           <t>weaponConfigPath</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>weaponTypeName</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>portraitAddress</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1400,6 +1412,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1560,6 +1582,16 @@
       <c r="AF3" t="inlineStr">
         <is>
           <t>武器配置资产工程路径（Assets/.../*.asset）</t>
+        </is>
+      </c>
+      <c r="AG3" s="1" t="inlineStr">
+        <is>
+          <t>主武器类型</t>
+        </is>
+      </c>
+      <c r="AH3" s="1" t="inlineStr">
+        <is>
+          <t>英雄头像 Addressables 地址</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1606,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>标准射击枪</t>
+          <t>紫苑</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1663,6 +1695,16 @@
       <c r="AF4" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/RifleGirl/RifleGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>自动步枪</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Portrait/RifleGirl</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1719,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>双持手枪</t>
+          <t>夜雀</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1766,6 +1808,16 @@
       <c r="AF5" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/DualPistolGirl/DualPistolGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>双持手枪</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Portrait/DualPistolGirl</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1832,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>霰弹枪</t>
+          <t>白凛</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1869,6 +1921,16 @@
       <c r="AF6" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/ShotgunGirl/ShotgunGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>霰弹枪</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Portrait/ShotgunGirl</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1945,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>精确手枪</t>
+          <t>隼音</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1972,6 +2034,16 @@
       <c r="AF7" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/PistolGirl/PistolGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>精确手枪</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Portrait/PistolGirl</t>
         </is>
       </c>
     </row>
@@ -1986,7 +2058,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>蓄力火箭筒</t>
+          <t>月兔</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2075,6 +2147,16 @@
       <c r="AF8" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/RocketLauncherGirl/RocketLauncherGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>蓄力火箭筒</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Portrait/RocketLauncherGirl</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2171,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>消防栓旋转枪</t>
+          <t>焰橙</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2178,6 +2260,16 @@
       <c r="AF9" t="inlineStr">
         <is>
           <t>Assets/GameResource/Weapons/MachineGunGirl/MachineGunGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>蓄力旋转机枪</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Portrait/MachineGunGirl</t>
         </is>
       </c>
     </row>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="4"/>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>蓄力火箭筒</t>
+          <t>快速爆破枪</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2270,6 +2270,119 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Portrait/MachineGunGirl</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BubbleGirl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>沫澜</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Character/BubbleGirl</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" t="n">
+        <v>40</v>
+      </c>
+      <c r="P10" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>30</v>
+      </c>
+      <c r="X10" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Assets/GameResource/Weapons/BubbleGirl/BubbleGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>满溢泡泡枪</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Portrait/BubbleGirl</t>
         </is>
       </c>
     </row>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>双持手枪</t>
+          <t>开尔文525</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>精确手枪</t>
+          <t>窄域标记枪</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1627,10 +1627,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4.313350251695304</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>8.626700503390607</v>
       </c>
       <c r="L4" t="n">
         <v>0.55</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>自动步枪</t>
+          <t>斯普拉射击枪</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1740,10 +1740,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>4.313350251695304</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>8.626700503390607</v>
       </c>
       <c r="L5" t="n">
         <v>0.55</v>
@@ -1853,10 +1853,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.313350251695304</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>8.626700503390607</v>
       </c>
       <c r="L6" t="n">
         <v>0.55</v>
@@ -1966,10 +1966,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>4.672796106003245</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>9.058035528560136</v>
       </c>
       <c r="L7" t="n">
         <v>0.55</v>
@@ -2079,10 +2079,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>4.313350251695304</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>8.626700503390607</v>
       </c>
       <c r="L8" t="n">
         <v>0.55</v>
@@ -2192,10 +2192,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J9" t="n">
-        <v>4.583333333333333</v>
+        <v>3.953904397387361</v>
       </c>
       <c r="K9" t="n">
-        <v>7.2</v>
+        <v>7.764030453051546</v>
       </c>
       <c r="L9" t="n">
         <v>0.55</v>
@@ -2305,10 +2305,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4.313350251695304</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>8.626700503390607</v>
       </c>
       <c r="L10" t="n">
         <v>0.55</v>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1036,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AM11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="22" customWidth="1" min="2" max="4"/>
@@ -1250,6 +1250,31 @@
           <t>portraitAddress</t>
         </is>
       </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>standingHeight</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>bodyRadius</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>compactHeight</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>controllerStepOffset</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>controllerSkinWidth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1422,6 +1447,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="75" customHeight="1">
       <c r="A3" s="1" t="inlineStr">
@@ -1592,6 +1642,31 @@
       <c r="AH3" s="1" t="inlineStr">
         <is>
           <t>英雄头像 Addressables 地址</t>
+        </is>
+      </c>
+      <c r="AI3" s="1" t="inlineStr">
+        <is>
+          <t>站立高度（米）</t>
+        </is>
+      </c>
+      <c r="AJ3" s="1" t="inlineStr">
+        <is>
+          <t>身体碰撞半径（米）</t>
+        </is>
+      </c>
+      <c r="AK3" s="1" t="inlineStr">
+        <is>
+          <t>潜墨碰撞高度（米）</t>
+        </is>
+      </c>
+      <c r="AL3" s="1" t="inlineStr">
+        <is>
+          <t>台阶高度（米）</t>
+        </is>
+      </c>
+      <c r="AM3" s="1" t="inlineStr">
+        <is>
+          <t>碰撞皮肤宽度（米）</t>
         </is>
       </c>
     </row>
@@ -1707,6 +1782,21 @@
           <t>Portrait/RifleGirl</t>
         </is>
       </c>
+      <c r="AI4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -1820,6 +1910,21 @@
           <t>Portrait/DualPistolGirl</t>
         </is>
       </c>
+      <c r="AI5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1853,10 +1958,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="J6" t="n">
-        <v>4.313350251695304</v>
+        <v>3.953904397387361</v>
       </c>
       <c r="K6" t="n">
-        <v>8.626700503390607</v>
+        <v>7.7640304530515465</v>
       </c>
       <c r="L6" t="n">
         <v>0.55</v>
@@ -1925,13 +2030,28 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>霰弹枪</t>
+          <t>爆炸泼桶</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Portrait/ShotgunGirl</t>
         </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="7">
@@ -2046,6 +2166,21 @@
           <t>Portrait/PistolGirl</t>
         </is>
       </c>
+      <c r="AI7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -2159,6 +2294,21 @@
           <t>Portrait/RocketLauncherGirl</t>
         </is>
       </c>
+      <c r="AI8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -2272,6 +2422,21 @@
           <t>Portrait/MachineGunGirl</t>
         </is>
       </c>
+      <c r="AI9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
@@ -2384,6 +2549,149 @@
         <is>
           <t>Portrait/BubbleGirl</t>
         </is>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SplooshGirl</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>铃芽</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Character/SplooshGirl</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>33.3333333333333</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.672796106003245</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.058035528560136</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>40</v>
+      </c>
+      <c r="P11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>30</v>
+      </c>
+      <c r="X11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Assets/GameResource/Weapons/SplooshGirl/SplooshGirlWeaponConfig.asset</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>广域标记枪</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Portrait/SplooshGirl</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -2500,19 +2500,19 @@
         </x:is>
       </x:c>
       <x:c r="AI11" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="AJ11" t="n">
+        <x:v>0.28</x:v>
+      </x:c>
+      <x:c r="AK11" t="n">
+        <x:v>0.625</x:v>
+      </x:c>
+      <x:c r="AL11" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="AK11" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="AL11" t="n">
-        <x:v>0.2</x:v>
-      </x:c>
       <x:c r="AM11" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.025</x:v>
       </x:c>
     </x:row>
     <x:row r="12">

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hero" sheetId="1" r:id="R9ab82206d8ce4c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hero" sheetId="1" r:id="Rd475515c67434a2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -898,6 +898,7 @@
     <x:col min="89" max="89" width="28" customWidth="1"/>
     <x:col min="90" max="90" width="28" customWidth="1"/>
     <x:col min="91" max="91" width="28" customWidth="1"/>
+    <x:col min="40" max="40" width="56" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -1096,6 +1097,9 @@
           <x:t xml:space="preserve">controllerSkinWidth</x:t>
         </x:is>
       </x:c>
+      <x:c r="AN1" t="str">
+        <x:v>subWeaponConfigPath</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="inlineStr">
@@ -1293,6 +1297,9 @@
           <x:t xml:space="preserve">float</x:t>
         </x:is>
       </x:c>
+      <x:c r="AN2" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="75" customHeight="1">
       <x:c r="A3" s="1" t="inlineStr">
@@ -1489,6 +1496,9 @@
         <x:is>
           <x:t xml:space="preserve">碰撞皮肤宽度（米）</x:t>
         </x:is>
+      </x:c>
+      <x:c r="AN3" t="str">
+        <x:v>副武器配置资产工程路径（可为空，Assets/.../*.asset）</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1618,6 +1628,9 @@
       <x:c r="AM4" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN4" t="str">
+        <x:v>Assets/GameResource/SubWeapons/Torpedo/TorpedoConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" t="n">
@@ -1746,6 +1759,9 @@
       <x:c r="AM5" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN5" t="str">
+        <x:v>Assets/GameResource/SubWeapons/SpeedPad/SpeedPadConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" t="n">
@@ -1874,6 +1890,9 @@
       <x:c r="AM6" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN6" t="str">
+        <x:v>Assets/GameResource/SubWeapons/JumpPad/JumpPadConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="B7" t="n">
@@ -2002,6 +2021,7 @@
       <x:c r="AM7" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="B8" t="n">
@@ -2130,6 +2150,9 @@
       <x:c r="AM8" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN8" t="str">
+        <x:v>Assets/GameResource/SubWeapons/CurlingBomb/CurlingBombConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="B9" t="n">
@@ -2258,6 +2281,9 @@
       <x:c r="AM9" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN9" t="str">
+        <x:v>Assets/GameResource/SubWeapons/InkCurtain/InkCurtainConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="B10" t="n">
@@ -2386,6 +2412,9 @@
       <x:c r="AM10" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN10" t="str">
+        <x:v>Assets/GameResource/SubWeapons/InkMine/InkMineConfig.asset</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="n">
@@ -2513,6 +2542,9 @@
       </x:c>
       <x:c r="AM11" t="n">
         <x:v>0.025</x:v>
+      </x:c>
+      <x:c r="AN11" t="str">
+        <x:v>Assets/GameResource/SubWeapons/Sprinkler/SprinklerConfig.asset</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2631,6 +2663,7 @@
       <x:c r="AM12" t="n">
         <x:v>0.03</x:v>
       </x:c>
+      <x:c r="AN12" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -2203,10 +2203,10 @@
         <ns0:v>33.3333333333333</ns0:v>
       </ns0:c>
       <ns0:c r="J9" t="n">
-        <ns0:v>3.953904397387361</ns0:v>
+        <ns0:v>4.313350251695303</ns0:v>
       </ns0:c>
       <ns0:c r="K9" t="n">
-        <ns0:v>7.764030453051546</ns0:v>
+        <ns0:v>8.626700503390605</ns0:v>
       </ns0:c>
       <ns0:c r="L9" t="n">
         <ns0:v>0.55</ns0:v>
@@ -2275,7 +2275,7 @@
       </ns0:c>
       <ns0:c r="AG9" t="inlineStr">
         <ns0:is>
-          <ns0:t xml:space="preserve">蓄力旋转机枪</ns0:t>
+          <ns0:t>斯普拉旋转枪</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AH9" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </ns0:c>
       <ns0:c r="AG11" t="inlineStr">
         <ns0:is>
-          <ns0:t xml:space="preserve">广域标记枪</ns0:t>
+          <ns0:t>专业模型枪MG</ns0:t>
         </ns0:is>
       </ns0:c>
       <ns0:c r="AH11" t="inlineStr">

--- a/Config/Luban/source/TbHero.xlsx
+++ b/Config/Luban/source/TbHero.xlsx
@@ -1577,10 +1577,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W4" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X4" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y4" t="n">
         <ns0:v>20</ns0:v>
@@ -1710,10 +1710,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W5" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X5" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y5" t="n">
         <ns0:v>20</ns0:v>
@@ -1843,10 +1843,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W6" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X6" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y6" t="n">
         <ns0:v>20</ns0:v>
@@ -1976,10 +1976,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W7" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X7" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y7" t="n">
         <ns0:v>20</ns0:v>
@@ -2109,10 +2109,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W8" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X8" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y8" t="n">
         <ns0:v>20</ns0:v>
@@ -2242,10 +2242,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W9" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X9" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y9" t="n">
         <ns0:v>20</ns0:v>
@@ -2375,10 +2375,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W10" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X10" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y10" t="n">
         <ns0:v>20</ns0:v>
@@ -2508,10 +2508,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W11" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X11" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y11" t="n">
         <ns0:v>20</ns0:v>
@@ -2636,10 +2636,10 @@
         <ns0:v>1</ns0:v>
       </ns0:c>
       <ns0:c r="W12" t="n">
-        <ns0:v>30</ns0:v>
+        <ns0:v>12.6</ns0:v>
       </ns0:c>
       <ns0:c r="X12" t="n">
-        <ns0:v>60</ns0:v>
+        <ns0:v>105</ns0:v>
       </ns0:c>
       <ns0:c r="Y12" t="n">
         <ns0:v>20</ns0:v>
